--- a/public/templates/Plexify_Lead_Import_Template.xlsx
+++ b/public/templates/Plexify_Lead_Import_Template.xlsx
@@ -398,19 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,6 +431,15 @@
       <c r="J1" t="str">
         <v>Notes</v>
       </c>
+      <c r="K1" t="str">
+        <v>City</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Country</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Phone</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -475,6 +472,15 @@
       <c r="J2" t="str">
         <v>Met at trade show booth</v>
       </c>
+      <c r="K2" t="str">
+        <v>New York</v>
+      </c>
+      <c r="L2" t="str">
+        <v>US</v>
+      </c>
+      <c r="M2" t="str">
+        <v>212-555-0142</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -507,23 +513,26 @@
       <c r="J3" t="str">
         <v/>
       </c>
+      <c r="K3" t="str">
+        <v>San Francisco</v>
+      </c>
+      <c r="L3" t="str">
+        <v>US</v>
+      </c>
+      <c r="M3" t="str">
+        <v>415-555-0198</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:D21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -777,9 +786,51 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>City</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C19" t="str">
+        <v>City, town, or municipality. Used for geographic filters and regional analysis. Headers auto-mapped: City, Town, Location, Locality.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Cleveland, San Francisco, New York</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Country</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Country name or ISO 3166-1 alpha-2 code. Normalized on import (USA / United States / U.S. -&gt; US). Headers auto-mapped: Country, Nation, Country Code.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>US, CA, GB</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Phone number in any format. Trimmed but not reformatted — preserves international formats. Headers auto-mapped: Phone, Phone Number, Tel, Telephone, Mobile, Cell.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>+1 212-555-0142, 415.555.0198, (020) 7946 0958</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
   </ignoredErrors>
 </worksheet>
 </file>